--- a/office/data/chart.xlsx
+++ b/office/data/chart.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cnplaman\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\office\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12362F83-1F52-4F10-A7C0-F1AEAE5B8DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5BBD436-C2D6-4E5B-996A-5C0C5DC89438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E30DA1E3-AF5B-4435-AC31-30C66707EE79}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E30DA1E3-AF5B-4435-AC31-30C66707EE79}"/>
   </bookViews>
   <sheets>
-    <sheet name="数据" sheetId="1" r:id="rId1"/>
-    <sheet name="柱形图" sheetId="2" r:id="rId2"/>
-    <sheet name="饼图" sheetId="3" r:id="rId3"/>
-    <sheet name="折线图" sheetId="4" r:id="rId4"/>
-    <sheet name="条形图" sheetId="5" r:id="rId5"/>
-    <sheet name="组合图" sheetId="7" r:id="rId6"/>
-    <sheet name="雷达图" sheetId="8" r:id="rId7"/>
-    <sheet name="迷你图" sheetId="9" r:id="rId8"/>
+    <sheet name="数据 Data" sheetId="1" r:id="rId1"/>
+    <sheet name="柱形图 Column" sheetId="2" r:id="rId2"/>
+    <sheet name="饼图 Pie" sheetId="3" r:id="rId3"/>
+    <sheet name="折线图 Line" sheetId="4" r:id="rId4"/>
+    <sheet name="条形图 Bar" sheetId="5" r:id="rId5"/>
+    <sheet name="堆积条形图 Stacked Bar" sheetId="11" r:id="rId6"/>
+    <sheet name="组合图 Combo" sheetId="7" r:id="rId7"/>
+    <sheet name="雷达图 Radar" sheetId="8" r:id="rId8"/>
+    <sheet name="迷你图 Mini" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -154,11 +155,59 @@
     <t>走势图</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>start</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>end</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>event</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>initial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>planing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>action</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>develop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>check</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>handover</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>closure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>duration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="179" formatCode="0_);[Red]\(0\)"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -198,8 +247,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -274,7 +332,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>数据!$B$1</c:f>
+              <c:f>'数据 Data'!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -359,7 +417,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>数据!$A$2:$A$7</c:f>
+              <c:f>'数据 Data'!$A$2:$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -385,7 +443,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>数据!$B$2:$B$7</c:f>
+              <c:f>'数据 Data'!$B$2:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -399,13 +457,13 @@
                   <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>18</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>19</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -421,7 +479,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>数据!$C$1</c:f>
+              <c:f>'数据 Data'!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -506,7 +564,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>数据!$A$2:$A$7</c:f>
+              <c:f>'数据 Data'!$A$2:$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -532,7 +590,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>数据!$C$2:$C$7</c:f>
+              <c:f>'数据 Data'!$C$2:$C$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -752,6 +810,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -759,7 +818,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -857,7 +915,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>数据!$C$1</c:f>
+              <c:f>'数据 Data'!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1206,7 +1264,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>数据!$A$2:$A$7</c:f>
+              <c:f>'数据 Data'!$A$2:$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -1232,7 +1290,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>数据!$C$2:$C$7</c:f>
+              <c:f>'数据 Data'!$C$2:$C$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -1315,6 +1373,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1322,7 +1381,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -1429,7 +1487,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>数据!$B$1</c:f>
+              <c:f>'数据 Data'!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1514,7 +1572,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>数据!$A$2:$A$7</c:f>
+              <c:f>'数据 Data'!$A$2:$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -1540,7 +1598,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>数据!$B$2:$B$7</c:f>
+              <c:f>'数据 Data'!$B$2:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -1554,13 +1612,13 @@
                   <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>18</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>19</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1577,7 +1635,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>数据!$C$1</c:f>
+              <c:f>'数据 Data'!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1662,7 +1720,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>数据!$A$2:$A$7</c:f>
+              <c:f>'数据 Data'!$A$2:$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -1688,7 +1746,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>数据!$C$2:$C$7</c:f>
+              <c:f>'数据 Data'!$C$2:$C$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -1892,6 +1950,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1899,7 +1958,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -2007,7 +2065,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>数据!$B$1</c:f>
+              <c:f>'数据 Data'!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2113,7 +2171,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>数据!$A$2:$A$7</c:f>
+              <c:f>'数据 Data'!$A$2:$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -2139,7 +2197,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>数据!$B$2:$B$7</c:f>
+              <c:f>'数据 Data'!$B$2:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -2153,13 +2211,13 @@
                   <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>18</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>19</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2175,7 +2233,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>数据!$C$1</c:f>
+              <c:f>'数据 Data'!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2281,7 +2339,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>数据!$A$2:$A$7</c:f>
+              <c:f>'数据 Data'!$A$2:$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -2307,7 +2365,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>数据!$C$2:$C$7</c:f>
+              <c:f>'数据 Data'!$C$2:$C$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -2497,6 +2555,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2504,7 +2563,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -2551,6 +2609,425 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'堆积条形图 Stacked Bar'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>start</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'堆积条形图 Stacked Bar'!$A$2:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>initial</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>planing</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>action</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>develop</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>check</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>handover</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>closure</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'堆积条形图 Stacked Bar'!$B$2:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>46073</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46075</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46143</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46204</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DBD2-4C54-99F5-6D08D29A05EC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'堆积条形图 Stacked Bar'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>duration</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>'堆积条形图 Stacked Bar'!$C$2:$C$8</c:f>
+              <c:numCache>
+                <c:formatCode>0_);[Red]\(0\)</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>14</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-DBD2-4C54-99F5-6D08D29A05EC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="1632174768"/>
+        <c:axId val="1632174288"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1632174768"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1632174288"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1632174288"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="46234"/>
+          <c:min val="46054"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="t"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1632174768"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="30"/>
+        <c:minorUnit val="10"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="zh-CN"/>
@@ -2612,7 +3089,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>数据!$B$1</c:f>
+              <c:f>'数据 Data'!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2717,7 +3194,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>数据!$A$2:$A$7</c:f>
+              <c:f>'数据 Data'!$A$2:$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -2743,7 +3220,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>数据!$B$2:$B$7</c:f>
+              <c:f>'数据 Data'!$B$2:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -2757,13 +3234,13 @@
                   <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>18</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>19</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2795,7 +3272,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>数据!$C$1</c:f>
+              <c:f>'数据 Data'!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2880,7 +3357,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>数据!$A$2:$A$7</c:f>
+              <c:f>'数据 Data'!$A$2:$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -2906,7 +3383,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>数据!$C$2:$C$7</c:f>
+              <c:f>'数据 Data'!$C$2:$C$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -3155,6 +3632,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3162,7 +3640,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -3208,7 +3685,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="zh-CN"/>
@@ -3262,7 +3739,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>数据!$B$1</c:f>
+              <c:f>'数据 Data'!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3291,7 +3768,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>数据!$A$2:$A$7</c:f>
+              <c:f>'数据 Data'!$A$2:$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -3317,7 +3794,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>数据!$B$2:$B$7</c:f>
+              <c:f>'数据 Data'!$B$2:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -3331,13 +3808,13 @@
                   <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>18</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>19</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3353,7 +3830,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>数据!$C$1</c:f>
+              <c:f>'数据 Data'!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3382,7 +3859,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>数据!$A$2:$A$7</c:f>
+              <c:f>'数据 Data'!$A$2:$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -3408,7 +3885,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>数据!$C$2:$C$7</c:f>
+              <c:f>'数据 Data'!$C$2:$C$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -3601,6 +4078,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3608,7 +4086,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3886,6 +4363,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="213">
   <cs:axisTitle>
@@ -5924,6 +6441,511 @@
 </file>
 
 <file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="328">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -6436,7 +7458,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="320">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7157,6 +8179,47 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>100012</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>557212</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="图表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D507B591-D76B-3903-5533-A913349E42F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>533400</xdr:colOff>
       <xdr:row>7</xdr:row>
@@ -7194,7 +8257,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -7533,13 +8596,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B832504-6F33-4500-A31B-74D9F7092472}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="9" max="9" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.25" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7550,7 +8623,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -7561,7 +8634,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -7572,7 +8645,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -7583,34 +8656,34 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5">
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C6">
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -7628,7 +8701,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C92D0F3-ADDB-47E7-9F32-7725596BB530}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7639,7 +8712,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C1AEFBB-18A6-4B9F-BD23-CC8ED66AE18C}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7650,7 +8723,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{802EFF5E-B453-497A-BD91-EA19A4DD0871}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7661,7 +8734,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E3FAF7C-2D11-49BD-9A10-EB5FB1A520DE}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7670,10 +8743,151 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{108307B9-CCE3-4633-A195-1ECD8D571D70}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE45E28F-E882-4FCF-A610-C94B58BB3FF1}">
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="1">
+        <v>46073</v>
+      </c>
+      <c r="C2" s="3">
+        <f>D2-B2</f>
+        <v>2</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="1">
+        <v>46075</v>
+      </c>
+      <c r="C3" s="3">
+        <f t="shared" ref="C3:C8" si="0">D3-B3</f>
+        <v>4</v>
+      </c>
+      <c r="D3" s="1">
+        <v>46079</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46076</v>
+      </c>
+      <c r="C4" s="3">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="D4" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="1">
+        <v>46078</v>
+      </c>
+      <c r="C5" s="3">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="D5" s="1">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="1">
+        <v>46143</v>
+      </c>
+      <c r="C6" s="3">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="D6" s="1">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="1">
+        <v>46174</v>
+      </c>
+      <c r="C7" s="3">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="D7" s="1">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="1">
+        <v>46204</v>
+      </c>
+      <c r="C8" s="3">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="D8" s="1">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H12" s="2">
+        <v>46000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H13" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H14" s="2">
+        <v>46234</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -7681,9 +8895,9 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB490177-721D-4F6C-9CE3-1F8EEB7BF3D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{108307B9-CCE3-4633-A195-1ECD8D571D70}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7692,14 +8906,25 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB490177-721D-4F6C-9CE3-1F8EEB7BF3D3}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CC767F6-168A-4387-9F88-6420C4B4DBBC}">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -7743,7 +8968,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -7784,7 +9009,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -7825,7 +9050,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -7866,7 +9091,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -7907,7 +9132,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -7948,7 +9173,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -7989,7 +9214,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -8030,7 +9255,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -8071,7 +9296,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -8112,7 +9337,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -8170,43 +9395,43 @@
           <x14:colorLow rgb="FFD00000"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>迷你图!B2:M2</xm:f>
+              <xm:f>'迷你图 Mini'!B2:M2</xm:f>
               <xm:sqref>N2</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>迷你图!B3:M3</xm:f>
+              <xm:f>'迷你图 Mini'!B3:M3</xm:f>
               <xm:sqref>N3</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>迷你图!B4:M4</xm:f>
+              <xm:f>'迷你图 Mini'!B4:M4</xm:f>
               <xm:sqref>N4</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>迷你图!B5:M5</xm:f>
+              <xm:f>'迷你图 Mini'!B5:M5</xm:f>
               <xm:sqref>N5</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>迷你图!B6:M6</xm:f>
+              <xm:f>'迷你图 Mini'!B6:M6</xm:f>
               <xm:sqref>N6</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>迷你图!B7:M7</xm:f>
+              <xm:f>'迷你图 Mini'!B7:M7</xm:f>
               <xm:sqref>N7</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>迷你图!B8:M8</xm:f>
+              <xm:f>'迷你图 Mini'!B8:M8</xm:f>
               <xm:sqref>N8</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>迷你图!B9:M9</xm:f>
+              <xm:f>'迷你图 Mini'!B9:M9</xm:f>
               <xm:sqref>N9</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>迷你图!B10:M10</xm:f>
+              <xm:f>'迷你图 Mini'!B10:M10</xm:f>
               <xm:sqref>N10</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>迷你图!B11:M11</xm:f>
+              <xm:f>'迷你图 Mini'!B11:M11</xm:f>
               <xm:sqref>N11</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>

--- a/office/data/chart.xlsx
+++ b/office/data/chart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\office\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5BBD436-C2D6-4E5B-996A-5C0C5DC89438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D95BC0BB-E333-448A-B64F-2C1C2948EF86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E30DA1E3-AF5B-4435-AC31-30C66707EE79}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{E30DA1E3-AF5B-4435-AC31-30C66707EE79}"/>
   </bookViews>
   <sheets>
     <sheet name="数据 Data" sheetId="1" r:id="rId1"/>
@@ -206,9 +206,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="179" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,21 +224,51 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -247,7 +277,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -257,8 +287,11 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8753,8 +8786,8 @@
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
         <v>35</v>
       </c>
       <c r="B1" t="s">
@@ -8767,8 +8800,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="1">
@@ -8782,8 +8815,8 @@
         <v>46075</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B3" s="1">
@@ -8797,8 +8830,8 @@
         <v>46079</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="4" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>38</v>
       </c>
       <c r="B4" s="1">
@@ -8812,8 +8845,8 @@
         <v>46083</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    <row r="5" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B5" s="1">
@@ -8827,8 +8860,8 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="6" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>40</v>
       </c>
       <c r="B6" s="1">
@@ -8842,8 +8875,8 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+    <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B7" s="1">
@@ -8857,8 +8890,8 @@
         <v>46204</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    <row r="8" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B8" s="1">
